--- a/测试集/边缘情况/下拉列表.xlsx
+++ b/测试集/边缘情况/下拉列表.xlsx
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1944.05</v>
+        <v>382.58</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>621.87</v>
+        <v>1221.5</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1925.88</v>
+        <v>343.66</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4136.12</v>
+        <v>1898.89</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2209.87</v>
+        <v>4360.23</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3431.12</v>
+        <v>3132.21</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2963.32</v>
+        <v>2335.05</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2890.05</v>
+        <v>3411.63</v>
       </c>
     </row>
   </sheetData>
